--- a/TestData/TMTT0005673_ActivitiesList_VerifyPreSetTemplateList.xlsx
+++ b/TestData/TMTT0005673_ActivitiesList_VerifyPreSetTemplateList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20393"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36C73E4-350A-4A21-8236-03F73AECE46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19018845-4498-4D05-B661-E13468D859CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18420" windowHeight="6456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -46,6 +46,9 @@
     <t>My Last 30 days Activities</t>
   </si>
   <si>
+    <t>Activities Filtered by Andrew B</t>
+  </si>
+  <si>
     <t>My Activities Today</t>
   </si>
   <si>
@@ -53,9 +56,6 @@
   </si>
   <si>
     <t>My Activities Yesterday</t>
-  </si>
-  <si>
-    <t>Activities Filtered by Andrew B</t>
   </si>
 </sst>
 </file>
@@ -99,9 +99,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,23 +422,23 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
+      <c r="A2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
